--- a/cucumber-for-appian/src/test/resources/testdata/End2End/02_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/02_NovatedApp_End2End.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="114">
   <si>
     <t>TC ID</t>
   </si>
@@ -288,6 +288,87 @@
   </si>
   <si>
     <t>REQ-730</t>
+  </si>
+  <si>
+    <t>CYP806</t>
+  </si>
+  <si>
+    <t>TESLA MODEL Y</t>
+  </si>
+  <si>
+    <t>8062</t>
+  </si>
+  <si>
+    <t>Neeti</t>
+  </si>
+  <si>
+    <t>Tripathi</t>
+  </si>
+  <si>
+    <t>03 Jul 1993</t>
+  </si>
+  <si>
+    <t>0499656877</t>
+  </si>
+  <si>
+    <t>neeti.tripathi@kmart.com.au.test</t>
+  </si>
+  <si>
+    <t>Kmart Australia Limited</t>
+  </si>
+  <si>
+    <t>29 Jul 2026</t>
+  </si>
+  <si>
+    <t>REQ-158</t>
+  </si>
+  <si>
+    <t>8063</t>
+  </si>
+  <si>
+    <t>REQ-159</t>
+  </si>
+  <si>
+    <t>8064</t>
+  </si>
+  <si>
+    <t>REQ-160</t>
+  </si>
+  <si>
+    <t>FTV21M</t>
+  </si>
+  <si>
+    <t>MAZDA CX-5</t>
+  </si>
+  <si>
+    <t>134449</t>
+  </si>
+  <si>
+    <t>Toshihiko</t>
+  </si>
+  <si>
+    <t>Inafune</t>
+  </si>
+  <si>
+    <t>05 Jun 1995</t>
+  </si>
+  <si>
+    <t>0469750861</t>
+  </si>
+  <si>
+    <t>inafune@jfcaust.com.au.test</t>
+  </si>
+  <si>
+    <t>JFC Australia Co Pty Ltd</t>
+  </si>
+  <si>
+    <t>20 Aug 2026</t>
+  </si>
+  <si>
+    <t>134450</t>
+  </si>
+  <si>
+    <t>REQ-1657</t>
   </si>
 </sst>
 </file>
@@ -1441,15 +1522,15 @@
         <v>37</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="D2" s="6" t="n">
         <f>C2+1</f>
-        <v>100704.0</v>
+        <v>134451.0</v>
       </c>
       <c r="E2" s="6" t="n">
         <f>D2</f>
-        <v>100704.0</v>
+        <v>134451.0</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>39</v>
@@ -1491,17 +1572,17 @@
         <v>42</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="V2" s="7" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>100,704 km</v>
+        <v>134,451 km</v>
       </c>
       <c r="W2" s="7" t="s">
         <v>46</v>
@@ -1510,39 +1591,39 @@
         <v>47</v>
       </c>
       <c r="Y2" s="7" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="Z2" s="7" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="AA2" s="7" t="str">
         <f>_xlfn.CONCAT(Y2," ",Z2)</f>
-        <v>David Cracknell</v>
+        <v>Toshihiko Inafune</v>
       </c>
       <c r="AB2" s="7" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AE2" s="7" t="s">
         <v>76</v>
       </c>
       <c r="AF2" s="7" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AG2" s="7" t="str">
         <f>AI2&amp;" - "&amp;AH2</f>
-        <v>VOLVO XC40 - FTJ63Y</v>
+        <v>MAZDA CX-5 - FTV21M</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="AI2" s="7" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="AJ2" s="7"/>
     </row>

--- a/cucumber-for-appian/src/test/resources/testdata/End2End/02_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/02_NovatedApp_End2End.xlsx
@@ -3,19 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhana\IdeaProjects\NovatedApp\cucumber-for-appian\src\test\resources\testdata\End2End\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CF1AB1-D870-4DFF-8499-190DC4986912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F3B245-97D0-48E2-B4FE-9EDD262BF897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="14" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="true"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="126">
   <si>
     <t>TC ID</t>
   </si>
@@ -399,19 +399,19 @@
     <t>AMP Capital Office and Industrial Pty Ltd</t>
   </si>
   <si>
-    <t>44099105094</t>
-  </si>
-  <si>
     <t>OYMJACPWRXEVYPYGENMAU CARLTON NSW 2218</t>
   </si>
   <si>
     <t>GVNMTQNAABTDB</t>
   </si>
   <si>
-    <t>ORI-243-419-983-156</t>
-  </si>
-  <si>
     <t>REQ-771</t>
+  </si>
+  <si>
+    <t>Estimated Annual Premium</t>
+  </si>
+  <si>
+    <t>TC004</t>
   </si>
 </sst>
 </file>
@@ -421,7 +421,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -442,6 +442,12 @@
       <color rgb="FF1F1F1F"/>
       <name val="Courier New"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -485,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -505,7 +511,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -802,32 +807,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BD10"/>
+  <dimension ref="A1:BE10"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="8.5"/>
-    <col min="2" max="2" customWidth="true" width="20.75"/>
-    <col min="3" max="4" customWidth="true" width="24.375"/>
-    <col min="5" max="5" customWidth="true" width="27.375"/>
-    <col min="6" max="6" customWidth="true" width="16.75"/>
-    <col min="7" max="7" customWidth="true" width="15.375"/>
-    <col min="8" max="8" customWidth="true" width="21.75"/>
-    <col min="9" max="9" customWidth="true" width="18.625"/>
-    <col min="10" max="10" customWidth="true" width="23.75"/>
-    <col min="11" max="11" customWidth="true" width="17.25"/>
-    <col min="12" max="12" customWidth="true" width="19.875"/>
-    <col min="13" max="13" customWidth="true" width="20.625"/>
-    <col min="14" max="14" customWidth="true" width="17.5"/>
-    <col min="15" max="15" customWidth="true" width="14.625"/>
-    <col min="16" max="16" customWidth="true" width="19.375"/>
-    <col min="17" max="17" customWidth="true" width="18.5"/>
-    <col min="18" max="23" customWidth="true" width="19.125"/>
-    <col min="51" max="51" style="1" width="8.875"/>
-    <col min="54" max="54" customWidth="true" width="14.625"/>
-    <col min="55" max="55" customWidth="true" width="17.375"/>
+    <col min="1" max="1" width="8.5" customWidth="1"/>
+    <col min="2" max="2" width="20.75" customWidth="1"/>
+    <col min="3" max="4" width="24.375" customWidth="1"/>
+    <col min="5" max="5" width="27.375" customWidth="1"/>
+    <col min="6" max="6" width="16.75" customWidth="1"/>
+    <col min="7" max="7" width="15.375" customWidth="1"/>
+    <col min="8" max="8" width="21.75" customWidth="1"/>
+    <col min="9" max="9" width="18.625" customWidth="1"/>
+    <col min="10" max="10" width="23.75" customWidth="1"/>
+    <col min="11" max="11" width="17.25" customWidth="1"/>
+    <col min="12" max="12" width="19.875" customWidth="1"/>
+    <col min="13" max="13" width="20.625" customWidth="1"/>
+    <col min="14" max="14" width="17.5" customWidth="1"/>
+    <col min="15" max="15" width="14.625" customWidth="1"/>
+    <col min="16" max="16" width="19.375" customWidth="1"/>
+    <col min="17" max="17" width="18.5" customWidth="1"/>
+    <col min="18" max="23" width="19.125" customWidth="1"/>
+    <col min="51" max="51" width="8.875" style="1"/>
+    <col min="54" max="54" width="14.625" customWidth="1"/>
+    <col min="55" max="55" width="17.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" s="1" customFormat="1" ht="67.5">
+    <row r="1" spans="1:57" s="1" customFormat="1" ht="67.5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -996,8 +1001,11 @@
       <c r="BD1" s="3" t="s">
         <v>114</v>
       </c>
+      <c r="BE1" s="3" t="s">
+        <v>124</v>
+      </c>
     </row>
-    <row r="2" spans="1:56" s="2" customFormat="1" ht="94.5">
+    <row r="2" spans="1:57" s="2" customFormat="1" ht="94.5">
       <c r="A2" s="4" t="s">
         <v>33</v>
       </c>
@@ -1016,13 +1024,13 @@
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(CLEAN(D2),"km",""),",","")," ",""),CHAR(160),"")</f>
         <v>18065</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="5">
         <f>E2+1</f>
-        <v>18066.0</v>
-      </c>
-      <c r="G2" s="5" t="n">
+        <v>18066</v>
+      </c>
+      <c r="G2" s="5">
         <f>F2</f>
-        <v>18066.0</v>
+        <v>18066</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>35</v>
@@ -1108,7 +1116,7 @@
         <v>57</v>
       </c>
       <c r="AI2" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AJ2" s="6" t="s">
         <v>85</v>
@@ -1130,7 +1138,7 @@
         <v>86</v>
       </c>
       <c r="AP2" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AQ2" s="6" t="s">
         <v>60</v>
@@ -1162,12 +1170,13 @@
       <c r="BB2" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="BC2" s="6" t="s">
-        <v>121</v>
+      <c r="BC2" s="6">
+        <v>44099105094</v>
       </c>
       <c r="BD2" s="6"/>
+      <c r="BE2" s="6"/>
     </row>
-    <row r="3" spans="1:56" s="2" customFormat="1" ht="81">
+    <row r="3" spans="1:57" s="2" customFormat="1" ht="81">
       <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
@@ -1304,7 +1313,7 @@
         <v>102</v>
       </c>
       <c r="AV3" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AW3" s="4" t="s">
         <v>103</v>
@@ -1328,8 +1337,9 @@
         <v>111</v>
       </c>
       <c r="BD3" s="4"/>
+      <c r="BE3" s="4"/>
     </row>
-    <row r="4" spans="1:56" ht="81">
+    <row r="4" spans="1:57" ht="81">
       <c r="A4" s="4" t="s">
         <v>105</v>
       </c>
@@ -1492,14 +1502,178 @@
       <c r="BD4" s="4" t="s">
         <v>113</v>
       </c>
+      <c r="BE4" s="4"/>
     </row>
-    <row r="5" spans="1:56">
-      <c r="E5" s="7"/>
+    <row r="5" spans="1:57" ht="81">
+      <c r="A5" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH5" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ5" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AL5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AM5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AN5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AO5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AP5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AQ5" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AR5" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="AS5" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AT5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="AU5" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="AV5" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="AW5" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AX5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AY5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AZ5" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BA5" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB5" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="BC5" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="BD5" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="BE5" s="4"/>
     </row>
-    <row r="10" spans="1:56" ht="14.25">
-      <c r="U10" s="8"/>
+    <row r="10" spans="1:57" ht="14.25">
+      <c r="U10" s="7"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cucumber-for-appian/src/test/resources/testdata/End2End/02_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/02_NovatedApp_End2End.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhana\IdeaProjects\NovatedApp\cucumber-for-appian\src\test\resources\testdata\End2End\"/>
     </mc:Choice>
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="TestData" sheetId="14" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="135">
   <si>
     <t>TC ID</t>
   </si>
@@ -412,6 +412,37 @@
   </si>
   <si>
     <t>TC004</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,079 km</t>
+  </si>
+  <si>
+    <t>0469 000 111</t>
+  </si>
+  <si>
+    <t>44099105094</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,186 km</t>
+  </si>
+  <si>
+    <t>ORI-829-620-384-687</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,199 km</t>
+  </si>
+  <si>
+    <t>ORI-311-256-293-415</t>
+  </si>
+  <si>
+    <t>Latest Reading (kms)
+21,202 km</t>
+  </si>
+  <si>
+    <t>ORI-214-723-536-390</t>
   </si>
 </sst>
 </file>
@@ -810,26 +841,26 @@
   <dimension ref="A1:BE10"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="8.5" customWidth="1"/>
-    <col min="2" max="2" width="20.75" customWidth="1"/>
-    <col min="3" max="4" width="24.375" customWidth="1"/>
-    <col min="5" max="5" width="27.375" customWidth="1"/>
-    <col min="6" max="6" width="16.75" customWidth="1"/>
-    <col min="7" max="7" width="15.375" customWidth="1"/>
-    <col min="8" max="8" width="21.75" customWidth="1"/>
-    <col min="9" max="9" width="18.625" customWidth="1"/>
-    <col min="10" max="10" width="23.75" customWidth="1"/>
-    <col min="11" max="11" width="17.25" customWidth="1"/>
-    <col min="12" max="12" width="19.875" customWidth="1"/>
-    <col min="13" max="13" width="20.625" customWidth="1"/>
-    <col min="14" max="14" width="17.5" customWidth="1"/>
-    <col min="15" max="15" width="14.625" customWidth="1"/>
-    <col min="16" max="16" width="19.375" customWidth="1"/>
-    <col min="17" max="17" width="18.5" customWidth="1"/>
-    <col min="18" max="23" width="19.125" customWidth="1"/>
-    <col min="51" max="51" width="8.875" style="1"/>
-    <col min="54" max="54" width="14.625" customWidth="1"/>
-    <col min="55" max="55" width="17.375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="8.5"/>
+    <col min="2" max="2" customWidth="true" width="20.75"/>
+    <col min="3" max="4" customWidth="true" width="24.375"/>
+    <col min="5" max="5" customWidth="true" width="27.375"/>
+    <col min="6" max="6" customWidth="true" width="16.75"/>
+    <col min="7" max="7" customWidth="true" width="15.375"/>
+    <col min="8" max="8" customWidth="true" width="21.75"/>
+    <col min="9" max="9" customWidth="true" width="18.625"/>
+    <col min="10" max="10" customWidth="true" width="23.75"/>
+    <col min="11" max="11" customWidth="true" width="17.25"/>
+    <col min="12" max="12" customWidth="true" width="19.875"/>
+    <col min="13" max="13" customWidth="true" width="20.625"/>
+    <col min="14" max="14" customWidth="true" width="17.5"/>
+    <col min="15" max="15" customWidth="true" width="14.625"/>
+    <col min="16" max="16" customWidth="true" width="19.375"/>
+    <col min="17" max="17" customWidth="true" width="18.5"/>
+    <col min="18" max="23" customWidth="true" width="19.125"/>
+    <col min="51" max="51" style="1" width="8.875"/>
+    <col min="54" max="54" customWidth="true" width="14.625"/>
+    <col min="55" max="55" customWidth="true" width="17.375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:57" s="1" customFormat="1" ht="67.5">
@@ -1013,24 +1044,24 @@
         <v>34</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D2" s="5" t="str">
         <f>SUBSTITUTE(C2,"Latest Reading (kms)","")</f>
         <v xml:space="preserve">
-18,065 km</v>
+21,202 km</v>
       </c>
       <c r="E2" s="5" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(CLEAN(D2),"km",""),",","")," ",""),CHAR(160),"")</f>
-        <v>18065</v>
-      </c>
-      <c r="F2" s="5">
+        <v>21202</v>
+      </c>
+      <c r="F2" s="5" t="n">
         <f>E2+1</f>
-        <v>18066</v>
-      </c>
-      <c r="G2" s="5">
+        <v>21203.0</v>
+      </c>
+      <c r="G2" s="5" t="n">
         <f>F2</f>
-        <v>18066</v>
+        <v>21203.0</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>35</v>
@@ -1085,7 +1116,7 @@
       </c>
       <c r="Y2" s="6" t="str">
         <f>TEXT(G2,"#,##0")&amp;" km"</f>
-        <v>18,066 km</v>
+        <v>21,203 km</v>
       </c>
       <c r="Z2" s="6" t="s">
         <v>38</v>
@@ -1107,7 +1138,7 @@
         <v>61</v>
       </c>
       <c r="AF2" s="6" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="AG2" s="6" t="s">
         <v>119</v>
@@ -1170,8 +1201,8 @@
       <c r="BB2" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="BC2" s="6">
-        <v>44099105094</v>
+      <c r="BC2" s="6" t="s">
+        <v>128</v>
       </c>
       <c r="BD2" s="6"/>
       <c r="BE2" s="6"/>
@@ -1313,7 +1344,7 @@
         <v>102</v>
       </c>
       <c r="AV3" s="4" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="AW3" s="4" t="s">
         <v>103</v>
